--- a/artfynd/A 9104-2026 artfynd.xlsx
+++ b/artfynd/A 9104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864856</v>
       </c>
       <c r="B2" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9104-2026 artfynd.xlsx
+++ b/artfynd/A 9104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864856</v>
       </c>
       <c r="B2" t="n">
-        <v>99553</v>
+        <v>99570</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9104-2026 artfynd.xlsx
+++ b/artfynd/A 9104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864856</v>
       </c>
       <c r="B2" t="n">
-        <v>99570</v>
+        <v>99571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9104-2026 artfynd.xlsx
+++ b/artfynd/A 9104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864856</v>
       </c>
       <c r="B2" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9104-2026 artfynd.xlsx
+++ b/artfynd/A 9104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864856</v>
       </c>
       <c r="B2" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9104-2026 artfynd.xlsx
+++ b/artfynd/A 9104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864856</v>
       </c>
       <c r="B2" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9104-2026 artfynd.xlsx
+++ b/artfynd/A 9104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135864856</v>
       </c>
       <c r="B2" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
